--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_magallanes_y_la_antartica_chilena.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>29.44191476941039</v>
+      </c>
+      <c r="C2">
         <v>27.55399883245768</v>
-      </c>
-      <c r="C2">
-        <v>29.44191476941039</v>
       </c>
       <c r="D2">
         <v>3.629237288135593</v>
       </c>
       <c r="E2">
-        <v>17.55077453947809</v>
+        <v>18.75330006618724</v>
       </c>
       <c r="F2">
         <v>63.69592539433467</v>
       </c>
       <c r="G2">
-        <v>18.75330006618724</v>
+        <v>17.55077453947809</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>41.75824175824176</v>
+      </c>
+      <c r="C3">
         <v>32.96703296703296</v>
-      </c>
-      <c r="C3">
-        <v>41.75824175824176</v>
       </c>
       <c r="D3">
         <v>3.033333333333333</v>
       </c>
       <c r="E3">
-        <v>18.86792452830189</v>
+        <v>23.89937106918239</v>
       </c>
       <c r="F3">
         <v>57.23270440251573</v>
       </c>
       <c r="G3">
-        <v>23.89937106918239</v>
+        <v>18.86792452830189</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>20.73170731707317</v>
+      </c>
+      <c r="C4">
         <v>28.04878048780488</v>
-      </c>
-      <c r="C4">
-        <v>20.73170731707317</v>
       </c>
       <c r="D4">
         <v>3.565217391304348</v>
       </c>
       <c r="E4">
-        <v>18.85245901639344</v>
+        <v>13.9344262295082</v>
       </c>
       <c r="F4">
         <v>67.21311475409836</v>
       </c>
       <c r="G4">
-        <v>13.9344262295082</v>
+        <v>18.85245901639344</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>41.7910447761194</v>
+      </c>
+      <c r="C5">
         <v>28.35820895522388</v>
-      </c>
-      <c r="C5">
-        <v>41.7910447761194</v>
       </c>
       <c r="D5">
         <v>3.526315789473684</v>
       </c>
       <c r="E5">
-        <v>16.66666666666667</v>
+        <v>24.56140350877192</v>
       </c>
       <c r="F5">
         <v>58.7719298245614</v>
       </c>
       <c r="G5">
-        <v>24.56140350877192</v>
+        <v>16.66666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>52.02520252025202</v>
+      </c>
+      <c r="C6">
         <v>11.52115211521152</v>
-      </c>
-      <c r="C6">
-        <v>52.02520252025202</v>
       </c>
       <c r="D6">
         <v>8.6796875</v>
       </c>
       <c r="E6">
-        <v>7.044578976334617</v>
+        <v>31.810676940011</v>
       </c>
       <c r="F6">
         <v>61.14474408365437</v>
       </c>
       <c r="G6">
-        <v>31.810676940011</v>
+        <v>7.044578976334617</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>32.20218319886094</v>
+      </c>
+      <c r="C7">
         <v>24.5609871855719</v>
-      </c>
-      <c r="C7">
-        <v>32.20218319886094</v>
       </c>
       <c r="D7">
         <v>4.071497584541063</v>
       </c>
       <c r="E7">
-        <v>15.66757493188011</v>
+        <v>20.54193157735392</v>
       </c>
       <c r="F7">
         <v>63.79049349076598</v>
       </c>
       <c r="G7">
-        <v>20.54193157735392</v>
+        <v>15.66757493188011</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>46.31828978622327</v>
+      </c>
+      <c r="C8">
         <v>26.84085510688836</v>
-      </c>
-      <c r="C8">
-        <v>46.31828978622327</v>
       </c>
       <c r="D8">
         <v>3.725663716814159</v>
       </c>
       <c r="E8">
-        <v>15.50068587105624</v>
+        <v>26.74897119341564</v>
       </c>
       <c r="F8">
         <v>57.75034293552812</v>
       </c>
       <c r="G8">
-        <v>26.74897119341563</v>
+        <v>15.50068587105624</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>32.91139240506329</v>
+      </c>
+      <c r="C9">
         <v>22.78481012658228</v>
-      </c>
-      <c r="C9">
-        <v>32.91139240506329</v>
       </c>
       <c r="D9">
         <v>4.388888888888889</v>
       </c>
       <c r="E9">
-        <v>14.63414634146342</v>
+        <v>21.13821138211382</v>
       </c>
       <c r="F9">
         <v>64.22764227642277</v>
       </c>
       <c r="G9">
-        <v>21.13821138211382</v>
+        <v>14.63414634146342</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>28.38452432870226</v>
+      </c>
+      <c r="C10">
         <v>28.70226154133699</v>
-      </c>
-      <c r="C10">
-        <v>28.38452432870226</v>
       </c>
       <c r="D10">
         <v>3.484046016930757</v>
       </c>
       <c r="E10">
-        <v>18.27159514555406</v>
+        <v>18.06932656460696</v>
       </c>
       <c r="F10">
         <v>63.65907828983898</v>
       </c>
       <c r="G10">
-        <v>18.06932656460696</v>
+        <v>18.27159514555406</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>18.81720430107527</v>
+      </c>
+      <c r="C11">
         <v>17.74193548387097</v>
-      </c>
-      <c r="C11">
-        <v>18.81720430107527</v>
       </c>
       <c r="D11">
         <v>5.636363636363637</v>
       </c>
       <c r="E11">
-        <v>12.99212598425197</v>
+        <v>13.77952755905512</v>
       </c>
       <c r="F11">
         <v>73.22834645669292</v>
       </c>
       <c r="G11">
-        <v>13.77952755905512</v>
+        <v>12.99212598425197</v>
       </c>
     </row>
   </sheetData>
